--- a/comparison_original_vs_reimpl.xlsx
+++ b/comparison_original_vs_reimpl.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.1 (-88.9%)</t>
+          <t>0.082 (-90.9%)</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.074 (-75.3%)</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.059 (-80.3%)</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.057 (-81.0%)</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.052 (-82.7%)</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.055 (-81.7%)</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.06 (-80.0%)</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.1 (-96.0%)</t>
+          <t>0.127 (-94.9%)</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.2 (-91.3%)</t>
+          <t>0.158 (-93.1%)</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.1 (-83.3%)</t>
+          <t>0.108 (-82.0%)</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.1 (-80.0%)</t>
+          <t>0.091 (-81.8%)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.097 (-67.7%)</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.1 (-75.0%)</t>
+          <t>0.105 (-73.8%)</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.1 (-75.0%)</t>
+          <t>0.09 (-77.5%)</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.1 (-98.1%)</t>
+          <t>0.113 (-97.9%)</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.3 (-94.4%)</t>
+          <t>0.253 (-95.3%)</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.2 (-84.6%)</t>
+          <t>0.249 (-80.8%)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.2 (-81.8%)</t>
+          <t>0.173 (-84.3%)</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.2 (-80.0%)</t>
+          <t>0.153 (-84.7%)</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.1 (-91.7%)</t>
+          <t>0.15 (-87.5%)</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.1 (-83.3%)</t>
+          <t>0.136 (-77.3%)</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.2 (-98.3%)</t>
+          <t>0.159 (-98.7%)</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.3 (-97.4%)</t>
+          <t>0.26 (-97.8%)</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.4 (-96.8%)</t>
+          <t>0.403 (-96.7%)</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.4 (-84.0%)</t>
+          <t>0.447 (-82.1%)</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.5 (-83.9%)</t>
+          <t>0.492 (-84.1%)</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.2 (-92.3%)</t>
+          <t>0.236 (-90.9%)</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.2 (-90.5%)</t>
+          <t>0.199 (-90.5%)</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.3 (-99.0%)</t>
+          <t>0.276 (-99.1%)</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.4 (-98.4%)</t>
+          <t>0.399 (-98.4%)</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.6 (-97.9%)</t>
+          <t>0.561 (-98.1%)</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.6 (-97.2%)</t>
+          <t>0.584 (-97.3%)</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.5 (-94.5%)</t>
+          <t>0.517 (-94.3%)</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.4 (-90.7%)</t>
+          <t>0.443 (-89.7%)</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.4 (-97.2%)</t>
+          <t>0.351 (-97.5%)</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.6 (-33.3%)</t>
+          <t>0.604 (-32.9%)</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.068 (-77.3%)</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.07 (-76.7%)</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.082 (-72.7%)</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.086 (-71.3%)</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.077 (-74.3%)</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.072 (-76.0%)</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2.2 (-12.0%)</t>
+          <t>2.181 (-12.8%)</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.2 (-66.7%)</t>
+          <t>0.249 (-58.5%)</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.2 (-60.0%)</t>
+          <t>0.197 (-60.6%)</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.134 (-55.3%)</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.2 (-50.0%)</t>
+          <t>0.157 (-60.8%)</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.2 (-50.0%)</t>
+          <t>0.189 (-52.8%)</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5.7 (+7.5%)</t>
+          <t>5.712 (+7.8%)</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4.2 (-22.2%)</t>
+          <t>4.229 (-21.7%)</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.6 (-53.8%)</t>
+          <t>0.625 (-51.9%)</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.6 (-45.5%)</t>
+          <t>0.582 (-47.1%)</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.7 (-30.0%)</t>
+          <t>0.659 (-34.1%)</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.8 (-33.3%)</t>
+          <t>0.805 (-32.9%)</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.3 (-50.0%)</t>
+          <t>0.311 (-48.2%)</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>12.4 (+5.1%)</t>
+          <t>12.38 (+4.9%)</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8.2 (-29.3%)</t>
+          <t>8.231 (-29.0%)</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>6.9 (-44.4%)</t>
+          <t>6.906 (-44.3%)</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1.0 (-60.0%)</t>
+          <t>1.007 (-59.7%)</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1.6 (-48.4%)</t>
+          <t>1.565 (-49.5%)</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1.4 (-46.2%)</t>
+          <t>1.45 (-44.2%)</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1.1 (-47.6%)</t>
+          <t>1.089 (-48.1%)</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>32.2 (+7.7%)</t>
+          <t>32.181 (+7.6%)</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>21.0 (-16.3%)</t>
+          <t>21.011 (-16.3%)</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>18.5 (-36.2%)</t>
+          <t>18.527 (-36.1%)</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>12.3 (-43.6%)</t>
+          <t>12.28 (-43.7%)</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5.5 (-39.6%)</t>
+          <t>5.503 (-39.5%)</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2.2 (-48.8%)</t>
+          <t>2.226 (-48.2%)</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>7.0 (-51.0%)</t>
+          <t>6.987 (-51.1%)</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1.3 (-60.6%)</t>
+          <t>1.317 (-60.1%)</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3.9 (+11.4%)</t>
+          <t>3.903 (+11.5%)</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1.7 (-63.0%)</t>
+          <t>1.663 (-63.8%)</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1.8 (-60.9%)</t>
+          <t>1.758 (-61.8%)</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2.5 (-45.7%)</t>
+          <t>2.456 (-46.6%)</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2.5 (-47.9%)</t>
+          <t>2.46 (-48.8%)</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1.9 (-50.0%)</t>
+          <t>1.931 (-49.2%)</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2.6 (-79.2%)</t>
+          <t>2.559 (-79.5%)</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5.6 (-51.3%)</t>
+          <t>5.565 (-51.6%)</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>6.0 (-39.4%)</t>
+          <t>5.99 (-39.5%)</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>5.5 (-58.3%)</t>
+          <t>5.455 (-58.7%)</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4.0 (-57.0%)</t>
+          <t>3.958 (-57.4%)</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3.7 (-54.3%)</t>
+          <t>3.704 (-54.3%)</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2.1 (-67.7%)</t>
+          <t>2.079 (-68.0%)</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>3.9 (-87.7%)</t>
+          <t>3.875 (-87.7%)</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6.2 (-77.7%)</t>
+          <t>6.177 (-77.8%)</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>12.6 (-11.9%)</t>
+          <t>12.603 (-11.9%)</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>11.6 (-26.1%)</t>
+          <t>11.601 (-26.1%)</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>6.4 (-54.3%)</t>
+          <t>6.395 (-54.3%)</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>4.9 (-59.5%)</t>
+          <t>4.871 (-59.7%)</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>5.5 (-97.1%)</t>
+          <t>5.536 (-97.1%)</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>5.8 (-90.3%)</t>
+          <t>5.838 (-90.2%)</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>9.3 (-83.0%)</t>
+          <t>9.305 (-83.0%)</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>14.8 (-58.7%)</t>
+          <t>14.752 (-58.8%)</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>13.0 (-42.0%)</t>
+          <t>13.038 (-41.8%)</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>11.3 (-37.2%)</t>
+          <t>11.343 (-37.0%)</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>10.1 (-45.1%)</t>
+          <t>10.075 (-45.2%)</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>10.3 (-68.2%)</t>
+          <t>10.286 (-68.3%)</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>14.1 (-87.8%)</t>
+          <t>14.098 (-87.8%)</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>17.7 (-84.2%)</t>
+          <t>17.741 (-84.1%)</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>26.4 (-61.8%)</t>
+          <t>26.356 (-61.9%)</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>26.0 (-14.8%)</t>
+          <t>25.953 (-14.9%)</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>17.7 (-45.9%)</t>
+          <t>17.663 (-46.0%)</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>21.2 (-76.9%)</t>
+          <t>21.174 (-76.9%)</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>17.1 (-36.7%)</t>
+          <t>17.106 (-36.6%)</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>1041 (+0.4%)</t>
+          <t>1044 (+0.7%)</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>263689 (+0.6%)</t>
+          <t>263969 (+0.7%)</t>
         </is>
       </c>
       <c r="H142" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1.3 (-64.9%)</t>
+          <t>0.579 (-84.4%)</t>
         </is>
       </c>
     </row>
@@ -5695,12 +5695,27 @@
       <c r="D143" t="n">
         <v>539</v>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>532 (-1.3%)</t>
+        </is>
+      </c>
       <c r="F143" t="n">
         <v>138667</v>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>137056 (-1.2%)</t>
+        </is>
+      </c>
       <c r="H143" t="n">
         <v>5.1</v>
       </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1.298 (-74.5%)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5717,12 +5732,27 @@
       <c r="D144" t="n">
         <v>362</v>
       </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>372 (+2.8%)</t>
+        </is>
+      </c>
       <c r="F144" t="n">
         <v>92744</v>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>93359 (+0.7%)</t>
+        </is>
+      </c>
       <c r="H144" t="n">
         <v>7.6</v>
       </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2.501 (-67.1%)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5739,12 +5769,27 @@
       <c r="D145" t="n">
         <v>280</v>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>282 (+0.7%)</t>
+        </is>
+      </c>
       <c r="F145" t="n">
         <v>72857</v>
       </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>72930 (+0.1%)</t>
+        </is>
+      </c>
       <c r="H145" t="n">
         <v>8.4</v>
       </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>3.39 (-59.6%)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5771,7 +5816,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>59365 (+0.2%)</t>
+          <t>59334 (+0.1%)</t>
         </is>
       </c>
       <c r="H146" t="n">
@@ -5779,7 +5824,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>7.9 (-25.5%)</t>
+          <t>4.417 (-58.3%)</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5861,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>0.0 (-100.0%)</t>
+          <t>0.046 (-92.3%)</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5898,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>0.0 (-100.0%)</t>
+          <t>0.049 (-94.6%)</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5935,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>0.1 (-88.9%)</t>
+          <t>0.064 (-92.9%)</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5972,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>0.1 (-88.9%)</t>
+          <t>0.086 (-90.4%)</t>
         </is>
       </c>
     </row>
@@ -5964,7 +6009,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>0.2 (-71.4%)</t>
+          <t>0.191 (-72.7%)</t>
         </is>
       </c>
     </row>
@@ -5997,11 +6042,11 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>0.5</v>
+        <v>0.2118</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>0.3 (-40.0%)</t>
+          <t>0.286 (+35.0%)</t>
         </is>
       </c>
     </row>
@@ -6034,11 +6079,11 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>0.9</v>
+        <v>0.6816</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>0.2 (-77.8%)</t>
+          <t>0.191 (-72.0%)</t>
         </is>
       </c>
     </row>
@@ -6071,11 +6116,11 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>2.8</v>
+        <v>2.362</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2.2 (-21.4%)</t>
+          <t>2.24 (-5.2%)</t>
         </is>
       </c>
     </row>
@@ -6108,11 +6153,11 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>8.1</v>
+        <v>6.961</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>7.3 (-9.9%)</t>
+          <t>7.31 (+5.0%)</t>
         </is>
       </c>
     </row>
@@ -6145,11 +6190,11 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>15.8</v>
+        <v>13.76</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>13.6 (-13.9%)</t>
+          <t>13.626 (-1.0%)</t>
         </is>
       </c>
     </row>
@@ -6182,11 +6227,11 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>20.7</v>
+        <v>18.09</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>17.8 (-14.0%)</t>
+          <t>17.772 (-1.8%)</t>
         </is>
       </c>
     </row>
@@ -6219,11 +6264,11 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>24.5</v>
+        <v>21.51</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>21.9 (-10.6%)</t>
+          <t>21.852 (+1.6%)</t>
         </is>
       </c>
     </row>
@@ -6256,11 +6301,11 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>0.9</v>
+        <v>0.34</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>0.7 (-22.2%)</t>
+          <t>0.736 (+116.5%)</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6338,11 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>1.6</v>
+        <v>1.593</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>0.5 (-68.8%)</t>
+          <t>0.5 (-68.6%)</t>
         </is>
       </c>
     </row>
@@ -6330,11 +6375,11 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>2.2</v>
+        <v>3.313</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>0.4 (-81.8%)</t>
+          <t>0.395 (-88.1%)</t>
         </is>
       </c>
     </row>
@@ -6367,11 +6412,11 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>2.5</v>
+        <v>4.039</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>0.9 (-64.0%)</t>
+          <t>0.939 (-76.8%)</t>
         </is>
       </c>
     </row>
@@ -6404,11 +6449,11 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>5</v>
+        <v>8.417</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>3.4 (-32.0%)</t>
+          <t>3.392 (-59.7%)</t>
         </is>
       </c>
     </row>
@@ -6441,11 +6486,11 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>7.8</v>
+        <v>13.18</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>5.0 (-35.9%)</t>
+          <t>5.032 (-61.8%)</t>
         </is>
       </c>
     </row>
@@ -6478,11 +6523,11 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>11</v>
+        <v>18.97</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>7.5 (-31.8%)</t>
+          <t>7.54 (-60.3%)</t>
         </is>
       </c>
     </row>
@@ -6515,11 +6560,11 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>1.5</v>
+        <v>0.5792</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>1.4 (-6.7%)</t>
+          <t>1.356 (+134.1%)</t>
         </is>
       </c>
     </row>
@@ -6552,11 +6597,11 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>2.1</v>
+        <v>2.089</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>1.0 (-52.4%)</t>
+          <t>1.015 (-51.4%)</t>
         </is>
       </c>
     </row>
@@ -6589,11 +6634,11 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>3.6</v>
+        <v>6.801</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>0.8 (-77.8%)</t>
+          <t>0.83 (-87.8%)</t>
         </is>
       </c>
     </row>
@@ -6626,11 +6671,11 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>3.1</v>
+        <v>7.174</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>0.6 (-80.6%)</t>
+          <t>0.584 (-91.9%)</t>
         </is>
       </c>
     </row>
@@ -6663,11 +6708,11 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>4.9</v>
+        <v>11.83</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>1.2 (-75.5%)</t>
+          <t>1.236 (-89.6%)</t>
         </is>
       </c>
     </row>
@@ -6700,11 +6745,11 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>6.6</v>
+        <v>16.31</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2.4 (-63.6%)</t>
+          <t>2.446 (-85.0%)</t>
         </is>
       </c>
     </row>
@@ -6737,11 +6782,11 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>7.9</v>
+        <v>19.63</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>4.3 (-45.6%)</t>
+          <t>4.333 (-77.9%)</t>
         </is>
       </c>
     </row>
@@ -6774,11 +6819,11 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>2.2</v>
+        <v>0.8767</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2.0 (-9.1%)</t>
+          <t>1.997 (+127.8%)</t>
         </is>
       </c>
     </row>
@@ -6811,11 +6856,11 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>3.1</v>
+        <v>3.015</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>1.5 (-51.6%)</t>
+          <t>1.545 (-48.8%)</t>
         </is>
       </c>
     </row>
@@ -6848,11 +6893,11 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>4.4</v>
+        <v>8.359</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>1.3 (-70.5%)</t>
+          <t>1.343 (-83.9%)</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6930,11 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>4.9</v>
+        <v>14.39</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>0.7 (-85.7%)</t>
+          <t>0.737 (-94.9%)</t>
         </is>
       </c>
     </row>
@@ -6922,11 +6967,11 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>6.8</v>
+        <v>21.25</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>0.9 (-86.8%)</t>
+          <t>0.892 (-95.8%)</t>
         </is>
       </c>
     </row>
@@ -6959,11 +7004,11 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>7.7</v>
+        <v>24.29</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>1.4 (-81.8%)</t>
+          <t>1.41 (-94.2%)</t>
         </is>
       </c>
     </row>
@@ -6996,11 +7041,11 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>8.800000000000001</v>
+        <v>27.69</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2.6 (-70.5%)</t>
+          <t>2.576 (-90.7%)</t>
         </is>
       </c>
     </row>
@@ -7033,11 +7078,11 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>3.3</v>
+        <v>1.294</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2.9 (-12.1%)</t>
+          <t>2.92 (+125.7%)</t>
         </is>
       </c>
     </row>
@@ -7070,11 +7115,11 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>5.3</v>
+        <v>5.174</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2.2 (-58.5%)</t>
+          <t>2.218 (-57.1%)</t>
         </is>
       </c>
     </row>
@@ -7107,11 +7152,11 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>5.6</v>
+        <v>10.56</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>1.9 (-66.1%)</t>
+          <t>1.881 (-82.2%)</t>
         </is>
       </c>
     </row>
@@ -7144,11 +7189,11 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>6.4</v>
+        <v>21.53</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>1.4 (-78.1%)</t>
+          <t>1.394 (-93.5%)</t>
         </is>
       </c>
     </row>
@@ -7181,11 +7226,11 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>9</v>
+        <v>33.92</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>0.9 (-90.0%)</t>
+          <t>0.931 (-97.3%)</t>
         </is>
       </c>
     </row>
@@ -7218,11 +7263,11 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>10.9</v>
+        <v>40.36</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>1.3 (-88.1%)</t>
+          <t>1.288 (-96.8%)</t>
         </is>
       </c>
     </row>
@@ -7255,11 +7300,11 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>10.1</v>
+        <v>40.47</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2.0 (-80.2%)</t>
+          <t>2.006 (-95.0%)</t>
         </is>
       </c>
     </row>
@@ -7292,11 +7337,11 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>0.2</v>
+        <v>0.06051</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>0.1 (-50.0%)</t>
+          <t>0.052 (-14.1%)</t>
         </is>
       </c>
     </row>
@@ -7329,11 +7374,11 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>0.2</v>
+        <v>0.1614</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>0.1 (-50.0%)</t>
+          <t>0.102 (-36.8%)</t>
         </is>
       </c>
     </row>
@@ -7366,11 +7411,11 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>2.4</v>
+        <v>1.948</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2.4 (+0.0%)</t>
+          <t>2.396 (+23.0%)</t>
         </is>
       </c>
     </row>
@@ -7403,11 +7448,11 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>8</v>
+        <v>6.71</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>8.0 (+0.0%)</t>
+          <t>8.003 (+19.3%)</t>
         </is>
       </c>
     </row>
@@ -7440,11 +7485,11 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>16.4</v>
+        <v>13.49</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>14.8 (-9.8%)</t>
+          <t>14.834 (+10.0%)</t>
         </is>
       </c>
     </row>
@@ -7477,11 +7522,11 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>20.6</v>
+        <v>17.43</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>19.9 (-3.4%)</t>
+          <t>19.921 (+14.3%)</t>
         </is>
       </c>
     </row>
@@ -7514,11 +7559,11 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>27.8</v>
+        <v>23.71</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>28.9 (+4.0%)</t>
+          <t>28.906 (+21.9%)</t>
         </is>
       </c>
     </row>
@@ -7551,11 +7596,11 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>0.4</v>
+        <v>0.1573</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>0.1 (-75.0%)</t>
+          <t>0.12 (-23.7%)</t>
         </is>
       </c>
     </row>
@@ -7588,11 +7633,11 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>0.4</v>
+        <v>0.3928</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>0.1 (-75.0%)</t>
+          <t>0.109 (-72.3%)</t>
         </is>
       </c>
     </row>
@@ -7625,11 +7670,11 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>0.5</v>
+        <v>0.7089</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>0.1 (-80.0%)</t>
+          <t>0.128 (-81.9%)</t>
         </is>
       </c>
     </row>
@@ -7662,11 +7707,11 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>0.6 (-40.0%)</t>
+          <t>0.648 (-61.1%)</t>
         </is>
       </c>
     </row>
@@ -7699,11 +7744,11 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>3.7</v>
+        <v>6.224</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>3.1 (-16.2%)</t>
+          <t>3.066 (-50.7%)</t>
         </is>
       </c>
     </row>
@@ -7736,11 +7781,11 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>6</v>
+        <v>10.15</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>5.1 (-15.0%)</t>
+          <t>5.125 (-49.5%)</t>
         </is>
       </c>
     </row>
@@ -7773,11 +7818,11 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>9.699999999999999</v>
+        <v>16.4</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>7.8 (-19.6%)</t>
+          <t>7.839 (-52.2%)</t>
         </is>
       </c>
     </row>
@@ -7810,11 +7855,11 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>0.8</v>
+        <v>0.3113</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>0.2 (-75.0%)</t>
+          <t>0.168 (-46.0%)</t>
         </is>
       </c>
     </row>
@@ -7847,11 +7892,11 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>0.7</v>
+        <v>0.6899</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>0.2 (-71.4%)</t>
+          <t>0.168 (-75.6%)</t>
         </is>
       </c>
     </row>
@@ -7884,11 +7929,11 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>0.7</v>
+        <v>1.384</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>0.2 (-71.4%)</t>
+          <t>0.172 (-87.6%)</t>
         </is>
       </c>
     </row>
@@ -7921,11 +7966,11 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>0.7</v>
+        <v>1.548</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>0.2 (-71.4%)</t>
+          <t>0.214 (-86.2%)</t>
         </is>
       </c>
     </row>
@@ -7958,11 +8003,11 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>1.6</v>
+        <v>4.005</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>1.0 (-37.5%)</t>
+          <t>1.018 (-74.6%)</t>
         </is>
       </c>
     </row>
@@ -7995,11 +8040,11 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>3</v>
+        <v>7.401</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2.2 (-26.7%)</t>
+          <t>2.187 (-70.4%)</t>
         </is>
       </c>
     </row>
@@ -8032,11 +8077,11 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>5.1</v>
+        <v>12.8</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>4.2 (-17.6%)</t>
+          <t>4.154 (-67.5%)</t>
         </is>
       </c>
     </row>
@@ -8069,11 +8114,11 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>1.4</v>
+        <v>0.5462</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>0.3 (-78.6%)</t>
+          <t>0.257 (-52.9%)</t>
         </is>
       </c>
     </row>
@@ -8106,11 +8151,11 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>1.2</v>
+        <v>1.116</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>0.2 (-83.3%)</t>
+          <t>0.245 (-78.0%)</t>
         </is>
       </c>
     </row>
@@ -8143,11 +8188,11 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>1.1</v>
+        <v>2.03</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>0.2 (-81.8%)</t>
+          <t>0.24 (-88.2%)</t>
         </is>
       </c>
     </row>
@@ -8180,11 +8225,11 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>0.9</v>
+        <v>2.537</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>0.3 (-66.7%)</t>
+          <t>0.259 (-89.8%)</t>
         </is>
       </c>
     </row>
@@ -8217,11 +8262,11 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>1.2</v>
+        <v>3.929</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>0.5 (-58.3%)</t>
+          <t>0.528 (-86.6%)</t>
         </is>
       </c>
     </row>
@@ -8254,11 +8299,11 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>2.1</v>
+        <v>6.761</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>1.2 (-42.9%)</t>
+          <t>1.231 (-81.8%)</t>
         </is>
       </c>
     </row>
@@ -8291,11 +8336,11 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>3.9</v>
+        <v>12.6</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2.3 (-41.0%)</t>
+          <t>2.268 (-82.0%)</t>
         </is>
       </c>
     </row>
@@ -8328,11 +8373,11 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>2</v>
+        <v>0.8025</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>0.4 (-80.0%)</t>
+          <t>0.384 (-52.1%)</t>
         </is>
       </c>
     </row>
@@ -8365,11 +8410,11 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>1.7</v>
+        <v>1.675</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>0.4 (-76.5%)</t>
+          <t>0.372 (-77.8%)</t>
         </is>
       </c>
     </row>
@@ -8402,11 +8447,11 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>1.5</v>
+        <v>2.755</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>0.4 (-73.3%)</t>
+          <t>0.395 (-85.7%)</t>
         </is>
       </c>
     </row>
@@ -8439,11 +8484,11 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>1.3</v>
+        <v>4.285</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>0.4 (-69.2%)</t>
+          <t>0.412 (-90.4%)</t>
         </is>
       </c>
     </row>
@@ -8476,11 +8521,11 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>1.3</v>
+        <v>4.931</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>0.6 (-53.8%)</t>
+          <t>0.603 (-87.8%)</t>
         </is>
       </c>
     </row>
@@ -8513,11 +8558,11 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>1.8</v>
+        <v>6.767</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>1.0 (-44.4%)</t>
+          <t>1.02 (-84.9%)</t>
         </is>
       </c>
     </row>
@@ -8550,11 +8595,11 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>3.1</v>
+        <v>12.3</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2.2 (-29.0%)</t>
+          <t>2.17 (-82.4%)</t>
         </is>
       </c>
     </row>
@@ -8587,11 +8632,11 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>0.5</v>
+        <v>0.2118</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>0.3 (-40.0%)</t>
+          <t>0.312 (+47.3%)</t>
         </is>
       </c>
     </row>
@@ -8624,11 +8669,11 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>0.9</v>
+        <v>0.6816</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>0.3 (-66.7%)</t>
+          <t>0.33 (-51.6%)</t>
         </is>
       </c>
     </row>
@@ -8661,11 +8706,11 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>2.8</v>
+        <v>2.362</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2.3 (-17.9%)</t>
+          <t>2.262 (-4.2%)</t>
         </is>
       </c>
     </row>
@@ -8698,11 +8743,11 @@
         </is>
       </c>
       <c r="H225" t="n">
-        <v>8.1</v>
+        <v>6.961</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>7.4 (-8.6%)</t>
+          <t>7.354 (+5.6%)</t>
         </is>
       </c>
     </row>
@@ -8735,11 +8780,11 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>15.8</v>
+        <v>13.76</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>14.4 (-8.9%)</t>
+          <t>14.429 (+4.9%)</t>
         </is>
       </c>
     </row>
@@ -8772,11 +8817,11 @@
         </is>
       </c>
       <c r="H227" t="n">
-        <v>20.7</v>
+        <v>18.09</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>18.6 (-10.1%)</t>
+          <t>18.592 (+2.8%)</t>
         </is>
       </c>
     </row>
@@ -8809,11 +8854,11 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>24.5</v>
+        <v>21.51</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>22.6 (-7.8%)</t>
+          <t>22.627 (+5.2%)</t>
         </is>
       </c>
     </row>
@@ -8846,11 +8891,11 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>0.9</v>
+        <v>0.34</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>0.6 (-33.3%)</t>
+          <t>0.633 (+86.2%)</t>
         </is>
       </c>
     </row>
@@ -8883,11 +8928,11 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>1.6</v>
+        <v>1.593</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>0.6 (-62.5%)</t>
+          <t>0.556 (-65.1%)</t>
         </is>
       </c>
     </row>
@@ -8920,11 +8965,11 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>2.2</v>
+        <v>3.313</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>0.5 (-77.3%)</t>
+          <t>0.515 (-84.5%)</t>
         </is>
       </c>
     </row>
@@ -8957,11 +9002,11 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>2.5</v>
+        <v>4.039</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>1.0 (-60.0%)</t>
+          <t>0.963 (-76.2%)</t>
         </is>
       </c>
     </row>
@@ -8994,11 +9039,11 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>5</v>
+        <v>8.417</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>3.5 (-30.0%)</t>
+          <t>3.488 (-58.6%)</t>
         </is>
       </c>
     </row>
@@ -9031,11 +9076,11 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>7.8</v>
+        <v>13.18</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>5.3 (-32.1%)</t>
+          <t>5.26 (-60.1%)</t>
         </is>
       </c>
     </row>
@@ -9068,11 +9113,11 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>11</v>
+        <v>18.97</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>7.4 (-32.7%)</t>
+          <t>7.446 (-60.7%)</t>
         </is>
       </c>
     </row>
@@ -9105,11 +9150,11 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>1.5</v>
+        <v>0.5792</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>1.1 (-26.7%)</t>
+          <t>1.089 (+88.0%)</t>
         </is>
       </c>
     </row>
@@ -9142,11 +9187,11 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>2.1</v>
+        <v>2.089</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>0.8 (-61.9%)</t>
+          <t>0.845 (-59.6%)</t>
         </is>
       </c>
     </row>
@@ -9179,11 +9224,11 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>3.6</v>
+        <v>6.801</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>0.8 (-77.8%)</t>
+          <t>0.789 (-88.4%)</t>
         </is>
       </c>
     </row>
@@ -9216,11 +9261,11 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>3.1</v>
+        <v>7.174</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>0.6 (-80.6%)</t>
+          <t>0.614 (-91.4%)</t>
         </is>
       </c>
     </row>
@@ -9253,11 +9298,11 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>4.9</v>
+        <v>11.83</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>1.4 (-71.4%)</t>
+          <t>1.43 (-87.9%)</t>
         </is>
       </c>
     </row>
@@ -9290,11 +9335,11 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>6.6</v>
+        <v>16.31</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2.6 (-60.6%)</t>
+          <t>2.637 (-83.8%)</t>
         </is>
       </c>
     </row>
@@ -9327,11 +9372,11 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>7.9</v>
+        <v>19.63</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>4.5 (-43.0%)</t>
+          <t>4.469 (-77.2%)</t>
         </is>
       </c>
     </row>
@@ -9364,11 +9409,11 @@
         </is>
       </c>
       <c r="H243" t="n">
-        <v>2.2</v>
+        <v>0.8767</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>1.7 (-22.7%)</t>
+          <t>1.701 (+94.0%)</t>
         </is>
       </c>
     </row>
@@ -9401,11 +9446,11 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>3.1</v>
+        <v>3.015</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>1.2 (-61.3%)</t>
+          <t>1.229 (-59.2%)</t>
         </is>
       </c>
     </row>
@@ -9438,11 +9483,11 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>4.4</v>
+        <v>8.359</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>1.0 (-77.3%)</t>
+          <t>1.038 (-87.6%)</t>
         </is>
       </c>
     </row>
@@ -9475,11 +9520,11 @@
         </is>
       </c>
       <c r="H246" t="n">
-        <v>4.9</v>
+        <v>14.39</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>0.8 (-83.7%)</t>
+          <t>0.752 (-94.8%)</t>
         </is>
       </c>
     </row>
@@ -9512,11 +9557,11 @@
         </is>
       </c>
       <c r="H247" t="n">
-        <v>6.8</v>
+        <v>21.25</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>1.0 (-85.3%)</t>
+          <t>1.037 (-95.1%)</t>
         </is>
       </c>
     </row>
@@ -9549,11 +9594,11 @@
         </is>
       </c>
       <c r="H248" t="n">
-        <v>7.7</v>
+        <v>24.29</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>1.7 (-77.9%)</t>
+          <t>1.713 (-92.9%)</t>
         </is>
       </c>
     </row>
@@ -9586,11 +9631,11 @@
         </is>
       </c>
       <c r="H249" t="n">
-        <v>8.800000000000001</v>
+        <v>27.69</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2.9 (-67.0%)</t>
+          <t>2.888 (-89.6%)</t>
         </is>
       </c>
     </row>
@@ -9623,11 +9668,11 @@
         </is>
       </c>
       <c r="H250" t="n">
-        <v>3.3</v>
+        <v>1.294</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2.4 (-27.3%)</t>
+          <t>2.367 (+82.9%)</t>
         </is>
       </c>
     </row>
@@ -9660,11 +9705,11 @@
         </is>
       </c>
       <c r="H251" t="n">
-        <v>5.3</v>
+        <v>5.174</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>1.8 (-66.0%)</t>
+          <t>1.815 (-64.9%)</t>
         </is>
       </c>
     </row>
@@ -9697,11 +9742,11 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>5.6</v>
+        <v>10.56</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>1.4 (-75.0%)</t>
+          <t>1.368 (-87.0%)</t>
         </is>
       </c>
     </row>
@@ -9734,11 +9779,11 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>6.4</v>
+        <v>21.53</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>1.0 (-84.4%)</t>
+          <t>1.0 (-95.4%)</t>
         </is>
       </c>
     </row>
@@ -9771,11 +9816,11 @@
         </is>
       </c>
       <c r="H254" t="n">
-        <v>9</v>
+        <v>33.92</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>1.0 (-88.9%)</t>
+          <t>0.975 (-97.1%)</t>
         </is>
       </c>
     </row>
@@ -9808,11 +9853,11 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>10.9</v>
+        <v>40.36</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>1.5 (-86.2%)</t>
+          <t>1.542 (-96.2%)</t>
         </is>
       </c>
     </row>
@@ -9845,11 +9890,11 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>10.1</v>
+        <v>40.47</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2.4 (-76.2%)</t>
+          <t>2.36 (-94.2%)</t>
         </is>
       </c>
     </row>
@@ -9882,11 +9927,11 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>0.2</v>
+        <v>0.06051</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>0.1 (-50.0%)</t>
+          <t>0.092 (+52.0%)</t>
         </is>
       </c>
     </row>
@@ -9919,11 +9964,11 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>0.2</v>
+        <v>0.1614</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>0.2 (+0.0%)</t>
+          <t>0.181 (+12.1%)</t>
         </is>
       </c>
     </row>
@@ -9956,11 +10001,11 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>2.4</v>
+        <v>1.948</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>2.7 (+12.5%)</t>
+          <t>2.688 (+38.0%)</t>
         </is>
       </c>
     </row>
@@ -9993,11 +10038,11 @@
         </is>
       </c>
       <c r="H260" t="n">
-        <v>8</v>
+        <v>6.71</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>8.7 (+8.7%)</t>
+          <t>8.718 (+29.9%)</t>
         </is>
       </c>
     </row>
@@ -10030,11 +10075,11 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>16.4</v>
+        <v>13.49</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>16.0 (-2.4%)</t>
+          <t>16.004 (+18.6%)</t>
         </is>
       </c>
     </row>
@@ -10067,11 +10112,11 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>20.6</v>
+        <v>17.43</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>21.3 (+3.4%)</t>
+          <t>21.273 (+22.0%)</t>
         </is>
       </c>
     </row>
@@ -10104,11 +10149,11 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>27.8</v>
+        <v>23.71</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>26.3 (-5.4%)</t>
+          <t>26.29 (+10.9%)</t>
         </is>
       </c>
     </row>
@@ -10141,11 +10186,11 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>0.4</v>
+        <v>0.1573</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>0.1 (-75.0%)</t>
+          <t>0.141 (-10.4%)</t>
         </is>
       </c>
     </row>
@@ -10178,11 +10223,11 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>0.4</v>
+        <v>0.3928</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>0.2 (-50.0%)</t>
+          <t>0.196 (-50.1%)</t>
         </is>
       </c>
     </row>
@@ -10215,11 +10260,11 @@
         </is>
       </c>
       <c r="H266" t="n">
-        <v>0.5</v>
+        <v>0.7089</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>0.3 (-40.0%)</t>
+          <t>0.261 (-63.2%)</t>
         </is>
       </c>
     </row>
@@ -10252,11 +10297,11 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>0.8 (-20.0%)</t>
+          <t>0.789 (-52.7%)</t>
         </is>
       </c>
     </row>
@@ -10289,11 +10334,11 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>3.7</v>
+        <v>6.224</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>3.1 (-16.2%)</t>
+          <t>3.12 (-49.9%)</t>
         </is>
       </c>
     </row>
@@ -10326,11 +10371,11 @@
         </is>
       </c>
       <c r="H269" t="n">
-        <v>6</v>
+        <v>10.15</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>4.9 (-18.3%)</t>
+          <t>4.907 (-51.7%)</t>
         </is>
       </c>
     </row>
@@ -10363,11 +10408,11 @@
         </is>
       </c>
       <c r="H270" t="n">
-        <v>9.699999999999999</v>
+        <v>16.4</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>7.9 (-18.6%)</t>
+          <t>7.907 (-51.8%)</t>
         </is>
       </c>
     </row>
@@ -10400,11 +10445,11 @@
         </is>
       </c>
       <c r="H271" t="n">
-        <v>0.8</v>
+        <v>0.3113</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>0.2 (-75.0%)</t>
+          <t>0.209 (-32.9%)</t>
         </is>
       </c>
     </row>
@@ -10437,11 +10482,11 @@
         </is>
       </c>
       <c r="H272" t="n">
-        <v>0.7</v>
+        <v>0.6899</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>0.3 (-57.1%)</t>
+          <t>0.258 (-62.6%)</t>
         </is>
       </c>
     </row>
@@ -10474,11 +10519,11 @@
         </is>
       </c>
       <c r="H273" t="n">
-        <v>0.7</v>
+        <v>1.384</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>0.4 (-42.9%)</t>
+          <t>0.37 (-73.3%)</t>
         </is>
       </c>
     </row>
@@ -10511,11 +10556,11 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>0.7</v>
+        <v>1.548</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>0.4 (-42.9%)</t>
+          <t>0.379 (-75.5%)</t>
         </is>
       </c>
     </row>
@@ -10548,11 +10593,11 @@
         </is>
       </c>
       <c r="H275" t="n">
-        <v>1.6</v>
+        <v>4.005</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>1.2 (-25.0%)</t>
+          <t>1.204 (-69.9%)</t>
         </is>
       </c>
     </row>
@@ -10585,11 +10630,11 @@
         </is>
       </c>
       <c r="H276" t="n">
-        <v>3</v>
+        <v>7.401</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>2.2 (-26.7%)</t>
+          <t>2.241 (-69.7%)</t>
         </is>
       </c>
     </row>
@@ -10622,11 +10667,11 @@
         </is>
       </c>
       <c r="H277" t="n">
-        <v>5.1</v>
+        <v>12.8</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>4.2 (-17.6%)</t>
+          <t>4.156 (-67.5%)</t>
         </is>
       </c>
     </row>
@@ -10659,11 +10704,11 @@
         </is>
       </c>
       <c r="H278" t="n">
-        <v>1.4</v>
+        <v>0.5462</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>0.3 (-78.6%)</t>
+          <t>0.299 (-45.3%)</t>
         </is>
       </c>
     </row>
@@ -10696,11 +10741,11 @@
         </is>
       </c>
       <c r="H279" t="n">
-        <v>1.2</v>
+        <v>1.116</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>0.3 (-75.0%)</t>
+          <t>0.344 (-69.2%)</t>
         </is>
       </c>
     </row>
@@ -10733,11 +10778,11 @@
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1.1</v>
+        <v>2.03</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>0.4 (-63.6%)</t>
+          <t>0.44 (-78.3%)</t>
         </is>
       </c>
     </row>
@@ -10770,11 +10815,11 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>0.9</v>
+        <v>2.537</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>0.5 (-44.4%)</t>
+          <t>0.466 (-81.6%)</t>
         </is>
       </c>
     </row>
@@ -10807,11 +10852,11 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>1.2</v>
+        <v>3.929</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>0.8 (-33.3%)</t>
+          <t>0.794 (-79.8%)</t>
         </is>
       </c>
     </row>
@@ -10844,11 +10889,11 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>2.1</v>
+        <v>6.761</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>1.5 (-28.6%)</t>
+          <t>1.496 (-77.9%)</t>
         </is>
       </c>
     </row>
@@ -10881,11 +10926,11 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>3.9</v>
+        <v>12.6</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>2.6 (-33.3%)</t>
+          <t>2.598 (-79.4%)</t>
         </is>
       </c>
     </row>
@@ -10918,11 +10963,11 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>2</v>
+        <v>0.8025</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>0.4 (-80.0%)</t>
+          <t>0.433 (-46.0%)</t>
         </is>
       </c>
     </row>
@@ -10955,11 +11000,11 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>1.7</v>
+        <v>1.675</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>0.5 (-70.6%)</t>
+          <t>0.498 (-70.3%)</t>
         </is>
       </c>
     </row>
@@ -10992,11 +11037,11 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>1.5</v>
+        <v>2.755</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>0.6 (-60.0%)</t>
+          <t>0.599 (-78.3%)</t>
         </is>
       </c>
     </row>
@@ -11029,11 +11074,11 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>1.3</v>
+        <v>4.285</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>0.8 (-38.5%)</t>
+          <t>0.767 (-82.1%)</t>
         </is>
       </c>
     </row>
@@ -11066,11 +11111,11 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>1.3</v>
+        <v>4.931</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>1.1 (-15.4%)</t>
+          <t>1.079 (-78.1%)</t>
         </is>
       </c>
     </row>
@@ -11103,11 +11148,11 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>1.8</v>
+        <v>6.767</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>1.2 (-33.3%)</t>
+          <t>1.23 (-81.8%)</t>
         </is>
       </c>
     </row>
@@ -11140,11 +11185,11 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>3.1</v>
+        <v>12.3</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>2.4 (-22.6%)</t>
+          <t>2.411 (-80.4%)</t>
         </is>
       </c>
     </row>
@@ -11177,11 +11222,11 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>0.5</v>
+        <v>0.2118</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>0.2 (-60.0%)</t>
+          <t>0.174 (-17.8%)</t>
         </is>
       </c>
     </row>
@@ -11214,11 +11259,11 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>0.9</v>
+        <v>0.6816</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>0.2 (-77.8%)</t>
+          <t>0.233 (-65.8%)</t>
         </is>
       </c>
     </row>
@@ -11251,11 +11296,11 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>2.8</v>
+        <v>2.362</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>2.5 (-10.7%)</t>
+          <t>2.45 (+3.7%)</t>
         </is>
       </c>
     </row>
@@ -11288,11 +11333,11 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>8.1</v>
+        <v>6.961</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>7.5 (-7.4%)</t>
+          <t>7.522 (+8.1%)</t>
         </is>
       </c>
     </row>
@@ -11325,11 +11370,11 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>15.8</v>
+        <v>13.76</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>14.9 (-5.7%)</t>
+          <t>14.86 (+8.0%)</t>
         </is>
       </c>
     </row>
@@ -11362,11 +11407,11 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>20.7</v>
+        <v>18.09</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>18.9 (-8.7%)</t>
+          <t>18.869 (+4.3%)</t>
         </is>
       </c>
     </row>
@@ -11399,11 +11444,11 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>24.5</v>
+        <v>21.51</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>23.4 (-4.5%)</t>
+          <t>23.352 (+8.6%)</t>
         </is>
       </c>
     </row>
@@ -11436,11 +11481,11 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>0.9</v>
+        <v>0.34</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>0.6 (-33.3%)</t>
+          <t>0.564 (+65.9%)</t>
         </is>
       </c>
     </row>
@@ -11473,11 +11518,11 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>1.6</v>
+        <v>1.593</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>0.4 (-75.0%)</t>
+          <t>0.413 (-74.1%)</t>
         </is>
       </c>
     </row>
@@ -11510,11 +11555,11 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>2.2</v>
+        <v>3.313</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>0.4 (-81.8%)</t>
+          <t>0.424 (-87.2%)</t>
         </is>
       </c>
     </row>
@@ -11547,11 +11592,11 @@
         </is>
       </c>
       <c r="H302" t="n">
-        <v>2.5</v>
+        <v>4.039</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>0.9 (-64.0%)</t>
+          <t>0.945 (-76.6%)</t>
         </is>
       </c>
     </row>
@@ -11584,11 +11629,11 @@
         </is>
       </c>
       <c r="H303" t="n">
-        <v>5</v>
+        <v>8.417</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>3.3 (-34.0%)</t>
+          <t>3.251 (-61.4%)</t>
         </is>
       </c>
     </row>
@@ -11621,11 +11666,11 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>7.8</v>
+        <v>13.18</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>5.2 (-33.3%)</t>
+          <t>5.18 (-60.7%)</t>
         </is>
       </c>
     </row>
@@ -11658,11 +11703,11 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>11</v>
+        <v>18.97</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>7.4 (-32.7%)</t>
+          <t>7.389 (-61.0%)</t>
         </is>
       </c>
     </row>
@@ -11695,11 +11740,11 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>1.5</v>
+        <v>0.5792</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>1.0 (-33.3%)</t>
+          <t>1.001 (+72.8%)</t>
         </is>
       </c>
     </row>
@@ -11732,11 +11777,11 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>2.1</v>
+        <v>2.089</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>0.8 (-61.9%)</t>
+          <t>0.758 (-63.7%)</t>
         </is>
       </c>
     </row>
@@ -11769,11 +11814,11 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>3.6</v>
+        <v>6.801</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>0.7 (-80.6%)</t>
+          <t>0.65 (-90.4%)</t>
         </is>
       </c>
     </row>
@@ -11806,11 +11851,11 @@
         </is>
       </c>
       <c r="H309" t="n">
-        <v>3.1</v>
+        <v>7.174</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>0.6 (-80.6%)</t>
+          <t>0.567 (-92.1%)</t>
         </is>
       </c>
     </row>
@@ -11843,11 +11888,11 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>4.9</v>
+        <v>11.83</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>1.4 (-71.4%)</t>
+          <t>1.378 (-88.4%)</t>
         </is>
       </c>
     </row>
@@ -11880,11 +11925,11 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>6.6</v>
+        <v>16.31</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>2.4 (-63.6%)</t>
+          <t>2.397 (-85.3%)</t>
         </is>
       </c>
     </row>
@@ -11917,11 +11962,11 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>7.9</v>
+        <v>19.63</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>4.4 (-44.3%)</t>
+          <t>4.443 (-77.4%)</t>
         </is>
       </c>
     </row>
@@ -11954,11 +11999,11 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>2.2</v>
+        <v>0.8767</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>1.7 (-22.7%)</t>
+          <t>1.735 (+97.9%)</t>
         </is>
       </c>
     </row>
@@ -11991,11 +12036,11 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>3.1</v>
+        <v>3.015</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>1.2 (-61.3%)</t>
+          <t>1.232 (-59.1%)</t>
         </is>
       </c>
     </row>
@@ -12028,11 +12073,11 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>4.4</v>
+        <v>8.359</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>1.0 (-77.3%)</t>
+          <t>0.964 (-88.5%)</t>
         </is>
       </c>
     </row>
@@ -12065,11 +12110,11 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>4.9</v>
+        <v>14.39</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>0.7 (-85.7%)</t>
+          <t>0.701 (-95.1%)</t>
         </is>
       </c>
     </row>
@@ -12102,11 +12147,11 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>6.8</v>
+        <v>21.25</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>1.0 (-85.3%)</t>
+          <t>0.99 (-95.3%)</t>
         </is>
       </c>
     </row>
@@ -12139,11 +12184,11 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>7.7</v>
+        <v>24.29</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>1.5 (-80.5%)</t>
+          <t>1.535 (-93.7%)</t>
         </is>
       </c>
     </row>
@@ -12176,11 +12221,11 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>8.800000000000001</v>
+        <v>27.69</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>2.8 (-68.2%)</t>
+          <t>2.752 (-90.1%)</t>
         </is>
       </c>
     </row>
@@ -12213,11 +12258,11 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>3.3</v>
+        <v>1.294</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>2.7 (-18.2%)</t>
+          <t>2.69 (+107.9%)</t>
         </is>
       </c>
     </row>
@@ -12250,11 +12295,11 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>5.3</v>
+        <v>5.174</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>1.8 (-66.0%)</t>
+          <t>1.825 (-64.7%)</t>
         </is>
       </c>
     </row>
@@ -12287,11 +12332,11 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>5.6</v>
+        <v>10.56</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>1.4 (-75.0%)</t>
+          <t>1.367 (-87.1%)</t>
         </is>
       </c>
     </row>
@@ -12324,11 +12369,11 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>6.4</v>
+        <v>21.53</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>0.9 (-85.9%)</t>
+          <t>0.946 (-95.6%)</t>
         </is>
       </c>
     </row>
@@ -12361,11 +12406,11 @@
         </is>
       </c>
       <c r="H324" t="n">
-        <v>9</v>
+        <v>33.92</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>0.9 (-90.0%)</t>
+          <t>0.945 (-97.2%)</t>
         </is>
       </c>
     </row>
@@ -12398,11 +12443,11 @@
         </is>
       </c>
       <c r="H325" t="n">
-        <v>10.9</v>
+        <v>40.36</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>1.4 (-87.2%)</t>
+          <t>1.357 (-96.6%)</t>
         </is>
       </c>
     </row>
@@ -12435,11 +12480,11 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>10.1</v>
+        <v>40.47</v>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>2.3 (-77.2%)</t>
+          <t>2.266 (-94.4%)</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12521,7 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>0.1 (-88.9%)</t>
+          <t>0.096 (-89.3%)</t>
         </is>
       </c>
     </row>
@@ -12513,7 +12558,7 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.062 (-79.3%)</t>
         </is>
       </c>
     </row>
@@ -12550,7 +12595,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.066 (-78.0%)</t>
         </is>
       </c>
     </row>
@@ -12587,7 +12632,7 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.064 (-78.7%)</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12669,7 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.065 (-78.3%)</t>
         </is>
       </c>
     </row>
@@ -12661,7 +12706,7 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.063 (-79.0%)</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12743,7 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.069 (-77.0%)</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12780,7 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>0.1 (-96.0%)</t>
+          <t>0.073 (-97.1%)</t>
         </is>
       </c>
     </row>
@@ -12772,7 +12817,7 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>0.1 (-95.7%)</t>
+          <t>0.084 (-96.3%)</t>
         </is>
       </c>
     </row>
@@ -12809,7 +12854,7 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>0.1 (-83.3%)</t>
+          <t>0.059 (-90.2%)</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12891,7 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>0.1 (-80.0%)</t>
+          <t>0.06 (-88.0%)</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12928,7 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.06 (-80.0%)</t>
         </is>
       </c>
     </row>
@@ -12920,7 +12965,7 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>0.1 (-75.0%)</t>
+          <t>0.061 (-84.8%)</t>
         </is>
       </c>
     </row>
@@ -12957,7 +13002,7 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>0.1 (-75.0%)</t>
+          <t>0.06 (-85.0%)</t>
         </is>
       </c>
     </row>
@@ -12994,7 +13039,7 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>0.1 (-98.1%)</t>
+          <t>0.086 (-98.4%)</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13076,7 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>0.1 (-98.1%)</t>
+          <t>0.108 (-98.0%)</t>
         </is>
       </c>
     </row>
@@ -13068,7 +13113,7 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>0.1 (-92.3%)</t>
+          <t>0.107 (-91.8%)</t>
         </is>
       </c>
     </row>
@@ -13105,7 +13150,7 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>0.1 (-90.9%)</t>
+          <t>0.093 (-91.5%)</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13187,7 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>0.1 (-90.0%)</t>
+          <t>0.09 (-91.0%)</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13224,7 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>0.1 (-91.7%)</t>
+          <t>0.092 (-92.3%)</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13261,7 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>0.1 (-83.3%)</t>
+          <t>0.085 (-85.8%)</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13298,7 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>0.1 (-99.2%)</t>
+          <t>0.112 (-99.1%)</t>
         </is>
       </c>
     </row>
@@ -13290,7 +13335,7 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>0.1 (-99.1%)</t>
+          <t>0.137 (-98.8%)</t>
         </is>
       </c>
     </row>
@@ -13327,7 +13372,7 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>0.2 (-98.4%)</t>
+          <t>0.177 (-98.6%)</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13409,7 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>0.1 (-96.0%)</t>
+          <t>0.139 (-94.4%)</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13446,7 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>0.1 (-96.8%)</t>
+          <t>0.137 (-95.6%)</t>
         </is>
       </c>
     </row>
@@ -13438,7 +13483,7 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>0.1 (-96.2%)</t>
+          <t>0.124 (-95.2%)</t>
         </is>
       </c>
     </row>
@@ -13475,7 +13520,7 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>0.1 (-95.2%)</t>
+          <t>0.119 (-94.3%)</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13557,7 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>0.3 (-99.0%)</t>
+          <t>0.303 (-99.0%)</t>
         </is>
       </c>
     </row>
@@ -13549,7 +13594,7 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>0.4 (-98.4%)</t>
+          <t>0.399 (-98.4%)</t>
         </is>
       </c>
     </row>
@@ -13586,7 +13631,7 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>0.4 (-98.6%)</t>
+          <t>0.419 (-98.6%)</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13668,7 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>0.4 (-98.2%)</t>
+          <t>0.378 (-98.3%)</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13705,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>0.3 (-96.7%)</t>
+          <t>0.332 (-96.4%)</t>
         </is>
       </c>
     </row>
@@ -13697,7 +13742,7 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>0.3 (-93.0%)</t>
+          <t>0.316 (-92.7%)</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13779,7 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>0.3 (-97.9%)</t>
+          <t>0.33 (-97.7%)</t>
         </is>
       </c>
     </row>
@@ -13771,7 +13816,7 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>0.7 (-22.2%)</t>
+          <t>0.65 (-27.8%)</t>
         </is>
       </c>
     </row>
@@ -13808,7 +13853,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.084 (-72.0%)</t>
         </is>
       </c>
     </row>
@@ -13845,7 +13890,7 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.079 (-73.7%)</t>
         </is>
       </c>
     </row>
@@ -13882,7 +13927,7 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.084 (-72.0%)</t>
         </is>
       </c>
     </row>
@@ -13919,7 +13964,7 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.083 (-72.3%)</t>
         </is>
       </c>
     </row>
@@ -13956,7 +14001,7 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.079 (-73.7%)</t>
         </is>
       </c>
     </row>
@@ -13993,7 +14038,7 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.079 (-73.7%)</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14112,7 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>0.6 (-73.9%)</t>
+          <t>0.564 (-75.5%)</t>
         </is>
       </c>
     </row>
@@ -14104,7 +14149,7 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>0.1 (-83.3%)</t>
+          <t>0.12 (-80.0%)</t>
         </is>
       </c>
     </row>
@@ -14141,7 +14186,7 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>0.1 (-80.0%)</t>
+          <t>0.097 (-80.6%)</t>
         </is>
       </c>
     </row>
@@ -14178,7 +14223,7 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>0.1 (-66.7%)</t>
+          <t>0.082 (-72.7%)</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14260,7 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>0.1 (-75.0%)</t>
+          <t>0.084 (-79.0%)</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14297,7 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>0.1 (-75.0%)</t>
+          <t>0.08 (-80.0%)</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14334,7 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>5.3 (+0.0%)</t>
+          <t>5.277 (-0.4%)</t>
         </is>
       </c>
     </row>
@@ -14326,7 +14371,7 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>2.0 (-63.0%)</t>
+          <t>2.046 (-62.1%)</t>
         </is>
       </c>
     </row>
@@ -14363,7 +14408,7 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>0.4 (-69.2%)</t>
+          <t>0.395 (-69.6%)</t>
         </is>
       </c>
     </row>
@@ -14400,7 +14445,7 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>0.2 (-81.8%)</t>
+          <t>0.207 (-81.2%)</t>
         </is>
       </c>
     </row>
@@ -14437,7 +14482,7 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>0.2 (-80.0%)</t>
+          <t>0.173 (-82.7%)</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14519,7 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>0.1 (-91.7%)</t>
+          <t>0.146 (-87.8%)</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14556,7 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>0.1 (-83.3%)</t>
+          <t>0.123 (-79.5%)</t>
         </is>
       </c>
     </row>
@@ -14548,7 +14593,7 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>11.1 (-5.9%)</t>
+          <t>11.083 (-6.1%)</t>
         </is>
       </c>
     </row>
@@ -14585,7 +14630,7 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>4.9 (-57.8%)</t>
+          <t>4.949 (-57.3%)</t>
         </is>
       </c>
     </row>
@@ -14622,7 +14667,7 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>1.9 (-84.7%)</t>
+          <t>1.913 (-84.6%)</t>
         </is>
       </c>
     </row>
@@ -14659,7 +14704,7 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>0.4 (-84.0%)</t>
+          <t>0.376 (-85.0%)</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14741,7 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>0.3 (-90.3%)</t>
+          <t>0.347 (-88.8%)</t>
         </is>
       </c>
     </row>
@@ -14733,7 +14778,7 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>0.3 (-88.5%)</t>
+          <t>0.253 (-90.3%)</t>
         </is>
       </c>
     </row>
@@ -14770,7 +14815,7 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>0.2 (-90.5%)</t>
+          <t>0.196 (-90.7%)</t>
         </is>
       </c>
     </row>
@@ -14807,7 +14852,7 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>18.6 (-37.8%)</t>
+          <t>18.59 (-37.8%)</t>
         </is>
       </c>
     </row>
@@ -14844,7 +14889,7 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>17.0 (-32.3%)</t>
+          <t>17.022 (-32.2%)</t>
         </is>
       </c>
     </row>
@@ -14881,7 +14926,7 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>7.3 (-74.8%)</t>
+          <t>7.303 (-74.8%)</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14963,7 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>1.4 (-93.6%)</t>
+          <t>1.375 (-93.7%)</t>
         </is>
       </c>
     </row>
@@ -14955,7 +15000,7 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>1.0 (-89.0%)</t>
+          <t>0.951 (-89.5%)</t>
         </is>
       </c>
     </row>
@@ -14992,7 +15037,7 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>1.0 (-76.7%)</t>
+          <t>1.001 (-76.7%)</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15074,7 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>0.6 (-95.8%)</t>
+          <t>0.556 (-96.1%)</t>
         </is>
       </c>
     </row>
@@ -15062,11 +15107,11 @@
         </is>
       </c>
       <c r="H397" t="n">
-        <v>874.3</v>
+        <v>347.9</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>870.5 (-0.4%)</t>
+          <t>870.514 (+150.2%)</t>
         </is>
       </c>
     </row>
@@ -15099,11 +15144,11 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>754.8</v>
+        <v>591.1</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>748.4 (-0.8%)</t>
+          <t>748.367 (+26.6%)</t>
         </is>
       </c>
     </row>
@@ -15136,11 +15181,11 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>699.6</v>
+        <v>580.6</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>701.7 (+0.3%)</t>
+          <t>701.695 (+20.9%)</t>
         </is>
       </c>
     </row>
@@ -15173,11 +15218,11 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>524.3</v>
+        <v>455.9</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>546.9 (+4.3%)</t>
+          <t>546.934 (+20.0%)</t>
         </is>
       </c>
     </row>
@@ -15210,11 +15255,11 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>469.7</v>
+        <v>405.6</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>451.5 (-3.9%)</t>
+          <t>451.538 (+11.3%)</t>
         </is>
       </c>
     </row>
@@ -15247,11 +15292,11 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>448.6</v>
+        <v>386.1</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>461.7 (+2.9%)</t>
+          <t>461.733 (+19.6%)</t>
         </is>
       </c>
     </row>
@@ -15284,11 +15329,11 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>444.5</v>
+        <v>393</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>434.3 (-2.3%)</t>
+          <t>434.345 (+10.5%)</t>
         </is>
       </c>
     </row>
@@ -15321,11 +15366,11 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>2117.7</v>
+        <v>842.7</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>879.9 (-58.5%)</t>
+          <t>879.895 (+4.4%)</t>
         </is>
       </c>
     </row>
@@ -15358,11 +15403,11 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>831</v>
+        <v>808.4</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>704.8 (-15.2%)</t>
+          <t>704.751 (-12.8%)</t>
         </is>
       </c>
     </row>
@@ -15395,11 +15440,11 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>549.9</v>
+        <v>851.3</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>558.6 (+1.6%)</t>
+          <t>558.588 (-34.4%)</t>
         </is>
       </c>
     </row>
@@ -15432,11 +15477,11 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>417.2</v>
+        <v>680.6</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>428.0 (+2.6%)</t>
+          <t>427.981 (-37.1%)</t>
         </is>
       </c>
     </row>
@@ -15469,11 +15514,11 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>357.2</v>
+        <v>600.4</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>356.3 (-0.3%)</t>
+          <t>356.313 (-40.7%)</t>
         </is>
       </c>
     </row>
@@ -15506,11 +15551,11 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>349.2</v>
+        <v>587.9</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>333.2 (-4.6%)</t>
+          <t>333.157 (-43.3%)</t>
         </is>
       </c>
     </row>
@@ -15543,11 +15588,11 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>313.3</v>
+        <v>540.2</v>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>338.5 (+8.0%)</t>
+          <t>338.47 (-37.3%)</t>
         </is>
       </c>
     </row>
@@ -15580,11 +15625,11 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>1922.7</v>
+        <v>765.4</v>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>879.4 (-54.3%)</t>
+          <t>879.436 (+14.9%)</t>
         </is>
       </c>
     </row>
@@ -15617,11 +15662,11 @@
         </is>
       </c>
       <c r="H412" t="n">
-        <v>808</v>
+        <v>786.8</v>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>709.1 (-12.2%)</t>
+          <t>709.069 (-9.9%)</t>
         </is>
       </c>
     </row>
@@ -15654,11 +15699,11 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>507.7</v>
+        <v>948.9</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>516.3 (+1.7%)</t>
+          <t>516.321 (-45.6%)</t>
         </is>
       </c>
     </row>
@@ -15691,11 +15736,11 @@
         </is>
       </c>
       <c r="H414" t="n">
-        <v>340.6</v>
+        <v>805.1</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>347.6 (+2.1%)</t>
+          <t>347.592 (-56.8%)</t>
         </is>
       </c>
     </row>
@@ -15728,11 +15773,11 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>276.3</v>
+        <v>685.6</v>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>300.4 (+8.7%)</t>
+          <t>300.355 (-56.2%)</t>
         </is>
       </c>
     </row>
@@ -15765,11 +15810,11 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>276.6</v>
+        <v>674.7</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>285.3 (+3.1%)</t>
+          <t>285.333 (-57.7%)</t>
         </is>
       </c>
     </row>
@@ -15802,11 +15847,11 @@
         </is>
       </c>
       <c r="H417" t="n">
-        <v>277.7</v>
+        <v>697.7</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>276.2 (-0.5%)</t>
+          <t>276.151 (-60.4%)</t>
         </is>
       </c>
     </row>
@@ -15839,11 +15884,11 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>1954.1</v>
+        <v>777.3</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>879.1 (-55.0%)</t>
+          <t>879.09 (+13.1%)</t>
         </is>
       </c>
     </row>
@@ -15876,11 +15921,11 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>865.5</v>
+        <v>842.7</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>710.6 (-17.9%)</t>
+          <t>710.635 (-15.7%)</t>
         </is>
       </c>
     </row>
@@ -15913,11 +15958,11 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>507.4</v>
+        <v>964.6</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>521.1 (+2.7%)</t>
+          <t>521.052 (-46.0%)</t>
         </is>
       </c>
     </row>
@@ -15950,11 +15995,11 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>307</v>
+        <v>905.7</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>309.2 (+0.7%)</t>
+          <t>309.208 (-65.9%)</t>
         </is>
       </c>
     </row>
@@ -15987,11 +16032,11 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>241.3</v>
+        <v>758.9</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>261.0 (+8.2%)</t>
+          <t>260.971 (-65.6%)</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16057,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>311 (-0.3%)</t>
+          <t>318 (+1.9%)</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -16020,15 +16065,15 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>51484 (-1.4%)</t>
+          <t>51569 (-1.2%)</t>
         </is>
       </c>
       <c r="H423" t="n">
-        <v>231.6</v>
+        <v>742.4</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>230.5 (-0.5%)</t>
+          <t>255.544 (-65.6%)</t>
         </is>
       </c>
     </row>
@@ -16061,11 +16106,11 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>242.1</v>
+        <v>754.3</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>237.6 (-1.9%)</t>
+          <t>237.55 (-68.5%)</t>
         </is>
       </c>
     </row>
@@ -16098,11 +16143,11 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>718.7</v>
+        <v>286</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>714.0 (-0.7%)</t>
+          <t>868.069 (+203.5%)</t>
         </is>
       </c>
     </row>
@@ -16135,11 +16180,11 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>760.8</v>
+        <v>740.8</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>712.3 (-6.4%)</t>
+          <t>712.346 (-3.8%)</t>
         </is>
       </c>
     </row>
@@ -16172,11 +16217,11 @@
         </is>
       </c>
       <c r="H427" t="n">
-        <v>511.1</v>
+        <v>969.9</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>518.4 (+1.4%)</t>
+          <t>518.446 (-46.5%)</t>
         </is>
       </c>
     </row>
@@ -16209,11 +16254,11 @@
         </is>
       </c>
       <c r="H428" t="n">
-        <v>277.5</v>
+        <v>937.5</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>284.0 (+2.3%)</t>
+          <t>284.015 (-69.7%)</t>
         </is>
       </c>
     </row>
@@ -16246,11 +16291,11 @@
         </is>
       </c>
       <c r="H429" t="n">
-        <v>233.8</v>
+        <v>847.1</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>231.4 (-1.0%)</t>
+          <t>231.402 (-72.7%)</t>
         </is>
       </c>
     </row>
@@ -16283,11 +16328,11 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>215.4</v>
+        <v>844.8</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>217.8 (+1.1%)</t>
+          <t>217.767 (-74.2%)</t>
         </is>
       </c>
     </row>
@@ -16320,11 +16365,11 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>218.6</v>
+        <v>850.5</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>223.2 (+2.1%)</t>
+          <t>223.156 (-73.8%)</t>
         </is>
       </c>
     </row>
@@ -16357,11 +16402,11 @@
         </is>
       </c>
       <c r="H432" t="n">
-        <v>851.3</v>
+        <v>338.9</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>880.1 (+3.4%)</t>
+          <t>880.113 (+159.7%)</t>
         </is>
       </c>
     </row>
@@ -16394,11 +16439,11 @@
         </is>
       </c>
       <c r="H433" t="n">
-        <v>738.7</v>
+        <v>574</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>743.2 (+0.6%)</t>
+          <t>743.188 (+29.5%)</t>
         </is>
       </c>
     </row>
@@ -16431,11 +16476,11 @@
         </is>
       </c>
       <c r="H434" t="n">
-        <v>691.2</v>
+        <v>558.8</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>693.0 (+0.3%)</t>
+          <t>693.012 (+24.0%)</t>
         </is>
       </c>
     </row>
@@ -16468,11 +16513,11 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>540.9</v>
+        <v>448.9</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>544.7 (+0.7%)</t>
+          <t>544.704 (+21.3%)</t>
         </is>
       </c>
     </row>
@@ -16505,11 +16550,11 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>482</v>
+        <v>398.7</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>469.9 (-2.5%)</t>
+          <t>469.926 (+17.9%)</t>
         </is>
       </c>
     </row>
@@ -16542,11 +16587,11 @@
         </is>
       </c>
       <c r="H437" t="n">
-        <v>452.6</v>
+        <v>378.1</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>453.7 (+0.2%)</t>
+          <t>453.745 (+20.0%)</t>
         </is>
       </c>
     </row>
@@ -16579,11 +16624,11 @@
         </is>
       </c>
       <c r="H438" t="n">
-        <v>444</v>
+        <v>372.5</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>439.0 (-1.1%)</t>
+          <t>438.981 (+17.8%)</t>
         </is>
       </c>
     </row>
@@ -16616,11 +16661,11 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>2050</v>
+        <v>816.4</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>876.2 (-57.3%)</t>
+          <t>876.162 (+7.3%)</t>
         </is>
       </c>
     </row>
@@ -16653,11 +16698,11 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>802.8</v>
+        <v>774.9</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>707.2 (-11.9%)</t>
+          <t>707.157 (-8.7%)</t>
         </is>
       </c>
     </row>
@@ -16690,11 +16735,11 @@
         </is>
       </c>
       <c r="H441" t="n">
-        <v>540</v>
+        <v>846.4</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>559.2 (+3.6%)</t>
+          <t>559.166 (-33.9%)</t>
         </is>
       </c>
     </row>
@@ -16727,11 +16772,11 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>401.7</v>
+        <v>662.8</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>417.7 (+4.0%)</t>
+          <t>417.69 (-37.0%)</t>
         </is>
       </c>
     </row>
@@ -16764,11 +16809,11 @@
         </is>
       </c>
       <c r="H443" t="n">
-        <v>359.3</v>
+        <v>593.9</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>359.0 (-0.1%)</t>
+          <t>358.97 (-39.6%)</t>
         </is>
       </c>
     </row>
@@ -16801,11 +16846,11 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>333.4</v>
+        <v>567.9</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>348.2 (+4.4%)</t>
+          <t>348.153 (-38.7%)</t>
         </is>
       </c>
     </row>
@@ -16838,11 +16883,11 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>327</v>
+        <v>554.2</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>333.1 (+1.9%)</t>
+          <t>333.119 (-39.9%)</t>
         </is>
       </c>
     </row>
@@ -16875,11 +16920,11 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>1945.3</v>
+        <v>774.4</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>857.2 (-55.9%)</t>
+          <t>857.235 (+10.7%)</t>
         </is>
       </c>
     </row>
@@ -16912,11 +16957,11 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>736.2</v>
+        <v>714.8</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>712.2 (-3.3%)</t>
+          <t>712.23 (-0.4%)</t>
         </is>
       </c>
     </row>
@@ -16949,11 +16994,11 @@
         </is>
       </c>
       <c r="H448" t="n">
-        <v>505</v>
+        <v>952.9</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>519.3 (+2.8%)</t>
+          <t>519.317 (-45.5%)</t>
         </is>
       </c>
     </row>
@@ -16972,11 +17017,26 @@
       <c r="D449" t="n">
         <v>439</v>
       </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>431 (-1.8%)</t>
+        </is>
+      </c>
       <c r="F449" t="n">
         <v>34682</v>
       </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>35379 (+2.0%)</t>
+        </is>
+      </c>
       <c r="H449" t="n">
-        <v>356.2</v>
+        <v>811.4</v>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>341.24 (-57.9%)</t>
+        </is>
       </c>
     </row>
     <row r="450">
@@ -16994,11 +17054,26 @@
       <c r="D450" t="n">
         <v>420</v>
       </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>414 (-1.4%)</t>
+        </is>
+      </c>
       <c r="F450" t="n">
         <v>58349</v>
       </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>60777 (+4.2%)</t>
+        </is>
+      </c>
       <c r="H450" t="n">
-        <v>303.1</v>
+        <v>721.7</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>289.091 (-59.9%)</t>
+        </is>
       </c>
     </row>
     <row r="451">
@@ -17016,11 +17091,26 @@
       <c r="D451" t="n">
         <v>398</v>
       </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>418 (+5.0%)</t>
+        </is>
+      </c>
       <c r="F451" t="n">
         <v>66856</v>
       </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>69333 (+3.7%)</t>
+        </is>
+      </c>
       <c r="H451" t="n">
-        <v>272</v>
+        <v>683.4</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>272.171 (-60.2%)</t>
+        </is>
       </c>
     </row>
     <row r="452">
@@ -17040,7 +17130,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>407 (+4.6%)</t>
+          <t>420 (+8.0%)</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -17048,15 +17138,15 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>76259 (+0.9%)</t>
+          <t>79071 (+4.6%)</t>
         </is>
       </c>
       <c r="H452" t="n">
-        <v>260.9</v>
+        <v>670.6</v>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>263.0 (+0.8%)</t>
+          <t>291.77 (-56.5%)</t>
         </is>
       </c>
     </row>
@@ -17089,11 +17179,11 @@
         </is>
       </c>
       <c r="H453" t="n">
-        <v>1953.1</v>
+        <v>777.8</v>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>861.4 (-55.9%)</t>
+          <t>861.362 (+10.7%)</t>
         </is>
       </c>
     </row>
@@ -17126,11 +17216,11 @@
         </is>
       </c>
       <c r="H454" t="n">
-        <v>837.4</v>
+        <v>812.2</v>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>714.3 (-14.7%)</t>
+          <t>714.317 (-12.1%)</t>
         </is>
       </c>
     </row>
@@ -17163,11 +17253,11 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>505.7</v>
+        <v>957.7</v>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>517.4 (+2.3%)</t>
+          <t>517.421 (-46.0%)</t>
         </is>
       </c>
     </row>
@@ -17200,11 +17290,11 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>295.3</v>
+        <v>860.9</v>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>317.4 (+7.5%)</t>
+          <t>317.38 (-63.1%)</t>
         </is>
       </c>
     </row>
@@ -17237,11 +17327,11 @@
         </is>
       </c>
       <c r="H457" t="n">
-        <v>240.4</v>
+        <v>746.6</v>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>260.8 (+8.5%)</t>
+          <t>260.806 (-65.1%)</t>
         </is>
       </c>
     </row>
@@ -17262,7 +17352,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>319 (+3.2%)</t>
+          <t>326 (+5.5%)</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -17270,15 +17360,15 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>53361 (+4.9%)</t>
+          <t>53279 (+4.7%)</t>
         </is>
       </c>
       <c r="H458" t="n">
-        <v>229.2</v>
+        <v>741.8</v>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>232.2 (+1.3%)</t>
+          <t>258.804 (-65.1%)</t>
         </is>
       </c>
     </row>
@@ -17311,11 +17401,11 @@
         </is>
       </c>
       <c r="H459" t="n">
-        <v>217.6</v>
+        <v>706.6</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>234.4 (+7.7%)</t>
+          <t>234.374 (-66.8%)</t>
         </is>
       </c>
     </row>
@@ -17348,11 +17438,11 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>713.2</v>
+        <v>283.9</v>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>678.5 (-4.9%)</t>
+          <t>855.615 (+201.4%)</t>
         </is>
       </c>
     </row>
@@ -17385,11 +17475,11 @@
         </is>
       </c>
       <c r="H461" t="n">
-        <v>698.4</v>
+        <v>678.1</v>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>701.6 (+0.5%)</t>
+          <t>701.58 (+3.5%)</t>
         </is>
       </c>
     </row>
@@ -17422,11 +17512,11 @@
         </is>
       </c>
       <c r="H462" t="n">
-        <v>508.4</v>
+        <v>966.6</v>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>519.6 (+2.2%)</t>
+          <t>519.56 (-46.2%)</t>
         </is>
       </c>
     </row>
@@ -17459,11 +17549,11 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>261.1</v>
+        <v>867.6</v>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>285.5 (+9.3%)</t>
+          <t>285.544 (-67.1%)</t>
         </is>
       </c>
     </row>
@@ -17484,7 +17574,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>277 (+0.7%)</t>
+          <t>276 (+0.4%)</t>
         </is>
       </c>
       <c r="F464" t="n">
@@ -17492,15 +17582,15 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>35837 (+5.8%)</t>
+          <t>36406 (+7.5%)</t>
         </is>
       </c>
       <c r="H464" t="n">
-        <v>204</v>
+        <v>741.9</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>211.6 (+3.7%)</t>
+          <t>235.764 (-68.2%)</t>
         </is>
       </c>
     </row>
@@ -17521,7 +17611,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>269 (+3.5%)</t>
+          <t>270 (+3.8%)</t>
         </is>
       </c>
       <c r="F465" t="n">
@@ -17529,15 +17619,15 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>43434 (+5.1%)</t>
+          <t>43815 (+6.0%)</t>
         </is>
       </c>
       <c r="H465" t="n">
-        <v>202.4</v>
+        <v>778.4</v>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>215.3 (+6.4%)</t>
+          <t>225.317 (-71.1%)</t>
         </is>
       </c>
     </row>
@@ -17558,7 +17648,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>286 (+14.9%)</t>
+          <t>278 (+11.6%)</t>
         </is>
       </c>
       <c r="F466" t="n">
@@ -17566,15 +17656,15 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>54282 (+8.3%)</t>
+          <t>52604 (+4.9%)</t>
         </is>
       </c>
       <c r="H466" t="n">
-        <v>190</v>
+        <v>763</v>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>208.7 (+9.8%)</t>
+          <t>226.802 (-70.3%)</t>
         </is>
       </c>
     </row>
@@ -17607,11 +17697,11 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>874.3</v>
+        <v>347.9</v>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>887.6 (+1.5%)</t>
+          <t>887.584 (+155.1%)</t>
         </is>
       </c>
     </row>
@@ -17644,11 +17734,11 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>754.8</v>
+        <v>591.1</v>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>747.6 (-1.0%)</t>
+          <t>747.629 (+26.5%)</t>
         </is>
       </c>
     </row>
@@ -17681,11 +17771,11 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>699.6</v>
+        <v>580.6</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>689.8 (-1.4%)</t>
+          <t>689.806 (+18.8%)</t>
         </is>
       </c>
     </row>
@@ -17718,11 +17808,11 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>524.3</v>
+        <v>455.9</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>536.9 (+2.4%)</t>
+          <t>536.853 (+17.8%)</t>
         </is>
       </c>
     </row>
@@ -17755,11 +17845,11 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>469.7</v>
+        <v>405.6</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>483.3 (+2.9%)</t>
+          <t>483.254 (+19.1%)</t>
         </is>
       </c>
     </row>
@@ -17792,11 +17882,11 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>448.6</v>
+        <v>386.1</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>448.4 (-0.0%)</t>
+          <t>448.447 (+16.1%)</t>
         </is>
       </c>
     </row>
@@ -17829,11 +17919,11 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>444.5</v>
+        <v>393</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>413.2 (-7.0%)</t>
+          <t>413.211 (+5.1%)</t>
         </is>
       </c>
     </row>
@@ -17866,11 +17956,11 @@
         </is>
       </c>
       <c r="H474" t="n">
-        <v>2117.7</v>
+        <v>842.7</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>867.7 (-59.0%)</t>
+          <t>867.737 (+3.0%)</t>
         </is>
       </c>
     </row>
@@ -17903,11 +17993,11 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>831</v>
+        <v>808.4</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>702.7 (-15.4%)</t>
+          <t>702.705 (-13.1%)</t>
         </is>
       </c>
     </row>
@@ -17940,11 +18030,11 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>549.9</v>
+        <v>851.3</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>557.7 (+1.4%)</t>
+          <t>557.712 (-34.5%)</t>
         </is>
       </c>
     </row>
@@ -17977,11 +18067,11 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>417.2</v>
+        <v>680.6</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>416.0 (-0.3%)</t>
+          <t>416.024 (-38.9%)</t>
         </is>
       </c>
     </row>
@@ -18014,11 +18104,11 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>357.2</v>
+        <v>600.4</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>366.5 (+2.6%)</t>
+          <t>366.474 (-39.0%)</t>
         </is>
       </c>
     </row>
@@ -18051,11 +18141,11 @@
         </is>
       </c>
       <c r="H479" t="n">
-        <v>349.2</v>
+        <v>587.9</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>339.5 (-2.8%)</t>
+          <t>339.53 (-42.2%)</t>
         </is>
       </c>
     </row>
@@ -18088,11 +18178,11 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>313.3</v>
+        <v>540.2</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>329.1 (+5.0%)</t>
+          <t>329.078 (-39.1%)</t>
         </is>
       </c>
     </row>
@@ -18125,11 +18215,11 @@
         </is>
       </c>
       <c r="H481" t="n">
-        <v>1922.7</v>
+        <v>765.4</v>
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>867.2 (-54.9%)</t>
+          <t>867.2 (+13.3%)</t>
         </is>
       </c>
     </row>
@@ -18162,11 +18252,11 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>808</v>
+        <v>786.8</v>
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>701.0 (-13.2%)</t>
+          <t>700.95 (-10.9%)</t>
         </is>
       </c>
     </row>
@@ -18199,11 +18289,11 @@
         </is>
       </c>
       <c r="H483" t="n">
-        <v>507.7</v>
+        <v>948.9</v>
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>519.1 (+2.2%)</t>
+          <t>519.11 (-45.3%)</t>
         </is>
       </c>
     </row>
@@ -18236,11 +18326,11 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>340.6</v>
+        <v>805.1</v>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>355.7 (+4.4%)</t>
+          <t>355.72 (-55.8%)</t>
         </is>
       </c>
     </row>
@@ -18273,11 +18363,11 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>276.3</v>
+        <v>685.6</v>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>299.6 (+8.4%)</t>
+          <t>299.568 (-56.3%)</t>
         </is>
       </c>
     </row>
@@ -18310,11 +18400,11 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>276.6</v>
+        <v>674.7</v>
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>289.6 (+4.7%)</t>
+          <t>289.587 (-57.1%)</t>
         </is>
       </c>
     </row>
@@ -18347,11 +18437,11 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>277.7</v>
+        <v>697.7</v>
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>269.0 (-3.1%)</t>
+          <t>269.048 (-61.4%)</t>
         </is>
       </c>
     </row>
@@ -18384,11 +18474,11 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>1954.1</v>
+        <v>777.3</v>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>871.8 (-55.4%)</t>
+          <t>871.823 (+12.2%)</t>
         </is>
       </c>
     </row>
@@ -18421,11 +18511,11 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>865.5</v>
+        <v>842.7</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>718.4 (-17.0%)</t>
+          <t>718.356 (-14.8%)</t>
         </is>
       </c>
     </row>
@@ -18458,11 +18548,11 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>507.4</v>
+        <v>964.6</v>
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>516.3 (+1.8%)</t>
+          <t>516.255 (-46.5%)</t>
         </is>
       </c>
     </row>
@@ -18495,11 +18585,11 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>307</v>
+        <v>905.7</v>
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>307.9 (+0.3%)</t>
+          <t>307.905 (-66.0%)</t>
         </is>
       </c>
     </row>
@@ -18532,11 +18622,11 @@
         </is>
       </c>
       <c r="H492" t="n">
-        <v>241.3</v>
+        <v>758.9</v>
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>255.1 (+5.7%)</t>
+          <t>255.06 (-66.4%)</t>
         </is>
       </c>
     </row>
@@ -18569,11 +18659,11 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>231.6</v>
+        <v>742.4</v>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>251.7 (+8.7%)</t>
+          <t>251.715 (-66.1%)</t>
         </is>
       </c>
     </row>
@@ -18606,11 +18696,11 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>242.1</v>
+        <v>754.3</v>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>240.2 (-0.8%)</t>
+          <t>240.239 (-68.2%)</t>
         </is>
       </c>
     </row>
@@ -18643,11 +18733,11 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>718.7</v>
+        <v>286</v>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>680.1 (-5.4%)</t>
+          <t>864.461 (+202.3%)</t>
         </is>
       </c>
     </row>
@@ -18680,11 +18770,11 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>760.8</v>
+        <v>740.8</v>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>717.6 (-5.7%)</t>
+          <t>717.61 (-3.1%)</t>
         </is>
       </c>
     </row>
@@ -18717,11 +18807,11 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>511.1</v>
+        <v>969.9</v>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>519.8 (+1.7%)</t>
+          <t>519.806 (-46.4%)</t>
         </is>
       </c>
     </row>
@@ -18754,11 +18844,11 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>277.5</v>
+        <v>937.5</v>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>284.1 (+2.4%)</t>
+          <t>284.052 (-69.7%)</t>
         </is>
       </c>
     </row>
@@ -18791,11 +18881,11 @@
         </is>
       </c>
       <c r="H499" t="n">
-        <v>233.8</v>
+        <v>847.1</v>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>229.1 (-2.0%)</t>
+          <t>229.116 (-73.0%)</t>
         </is>
       </c>
     </row>
@@ -18828,11 +18918,11 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>215.4</v>
+        <v>844.8</v>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>224.0 (+4.0%)</t>
+          <t>224.021 (-73.5%)</t>
         </is>
       </c>
     </row>
@@ -18865,11 +18955,11 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>218.6</v>
+        <v>850.5</v>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>214.8 (-1.7%)</t>
+          <t>214.793 (-74.7%)</t>
         </is>
       </c>
     </row>
@@ -18902,11 +18992,11 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>851.3</v>
+        <v>338.9</v>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>880.2 (+3.4%)</t>
+          <t>880.192 (+159.7%)</t>
         </is>
       </c>
     </row>
@@ -18939,11 +19029,11 @@
         </is>
       </c>
       <c r="H503" t="n">
-        <v>738.7</v>
+        <v>574</v>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>739.3 (+0.1%)</t>
+          <t>739.339 (+28.8%)</t>
         </is>
       </c>
     </row>
@@ -18976,11 +19066,11 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>691.2</v>
+        <v>558.8</v>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>695.6 (+0.6%)</t>
+          <t>695.637 (+24.5%)</t>
         </is>
       </c>
     </row>
@@ -19013,11 +19103,11 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>540.9</v>
+        <v>448.9</v>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>554.0 (+2.4%)</t>
+          <t>553.969 (+23.4%)</t>
         </is>
       </c>
     </row>
@@ -19050,11 +19140,11 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>482</v>
+        <v>398.7</v>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>476.4 (-1.2%)</t>
+          <t>476.37 (+19.5%)</t>
         </is>
       </c>
     </row>
@@ -19087,11 +19177,11 @@
         </is>
       </c>
       <c r="H507" t="n">
-        <v>452.6</v>
+        <v>378.1</v>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>442.6 (-2.2%)</t>
+          <t>442.613 (+17.1%)</t>
         </is>
       </c>
     </row>
@@ -19124,11 +19214,11 @@
         </is>
       </c>
       <c r="H508" t="n">
-        <v>444</v>
+        <v>372.5</v>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>429.1 (-3.4%)</t>
+          <t>429.067 (+15.2%)</t>
         </is>
       </c>
     </row>
@@ -19161,11 +19251,11 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>2050</v>
+        <v>816.4</v>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>874.2 (-57.4%)</t>
+          <t>874.203 (+7.1%)</t>
         </is>
       </c>
     </row>
@@ -19198,11 +19288,11 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>802.8</v>
+        <v>774.9</v>
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>705.3 (-12.1%)</t>
+          <t>705.261 (-9.0%)</t>
         </is>
       </c>
     </row>
@@ -19235,11 +19325,11 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>540</v>
+        <v>846.4</v>
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>559.3 (+3.6%)</t>
+          <t>559.302 (-33.9%)</t>
         </is>
       </c>
     </row>
@@ -19272,11 +19362,11 @@
         </is>
       </c>
       <c r="H512" t="n">
-        <v>401.7</v>
+        <v>662.8</v>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>408.8 (+1.8%)</t>
+          <t>408.78 (-38.3%)</t>
         </is>
       </c>
     </row>
@@ -19309,11 +19399,11 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>359.3</v>
+        <v>593.9</v>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>356.2 (-0.9%)</t>
+          <t>356.163 (-40.0%)</t>
         </is>
       </c>
     </row>
@@ -19346,11 +19436,11 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>333.4</v>
+        <v>567.9</v>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>352.1 (+5.6%)</t>
+          <t>352.148 (-38.0%)</t>
         </is>
       </c>
     </row>
@@ -19383,11 +19473,11 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>327</v>
+        <v>554.2</v>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>323.7 (-1.0%)</t>
+          <t>323.671 (-41.6%)</t>
         </is>
       </c>
     </row>
@@ -19420,11 +19510,11 @@
         </is>
       </c>
       <c r="H516" t="n">
-        <v>1945.3</v>
+        <v>774.4</v>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>857.3 (-55.9%)</t>
+          <t>857.279 (+10.7%)</t>
         </is>
       </c>
     </row>
@@ -19457,11 +19547,11 @@
         </is>
       </c>
       <c r="H517" t="n">
-        <v>736.2</v>
+        <v>714.8</v>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>711.3 (-3.4%)</t>
+          <t>711.349 (-0.5%)</t>
         </is>
       </c>
     </row>
@@ -19494,11 +19584,11 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>505</v>
+        <v>952.9</v>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>517.4 (+2.5%)</t>
+          <t>517.415 (-45.7%)</t>
         </is>
       </c>
     </row>
@@ -19531,11 +19621,11 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>356.2</v>
+        <v>811.4</v>
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>353.4 (-0.8%)</t>
+          <t>353.415 (-56.4%)</t>
         </is>
       </c>
     </row>
@@ -19568,11 +19658,11 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>303.1</v>
+        <v>721.7</v>
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>303.2 (+0.0%)</t>
+          <t>303.182 (-58.0%)</t>
         </is>
       </c>
     </row>
@@ -19605,11 +19695,11 @@
         </is>
       </c>
       <c r="H521" t="n">
-        <v>272</v>
+        <v>683.4</v>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>287.3 (+5.6%)</t>
+          <t>287.267 (-58.0%)</t>
         </is>
       </c>
     </row>
@@ -19642,11 +19732,11 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>260.9</v>
+        <v>670.6</v>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>268.1 (+2.8%)</t>
+          <t>268.142 (-60.0%)</t>
         </is>
       </c>
     </row>
@@ -19679,11 +19769,11 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>1953.1</v>
+        <v>777.8</v>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>864.4 (-55.7%)</t>
+          <t>864.399 (+11.1%)</t>
         </is>
       </c>
     </row>
@@ -19716,11 +19806,11 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>837.4</v>
+        <v>812.2</v>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>710.4 (-15.2%)</t>
+          <t>710.44 (-12.5%)</t>
         </is>
       </c>
     </row>
@@ -19753,11 +19843,11 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>505.7</v>
+        <v>957.7</v>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>517.5 (+2.3%)</t>
+          <t>517.485 (-46.0%)</t>
         </is>
       </c>
     </row>
@@ -19790,11 +19880,11 @@
         </is>
       </c>
       <c r="H526" t="n">
-        <v>295.3</v>
+        <v>860.9</v>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>315.6 (+6.9%)</t>
+          <t>315.611 (-63.3%)</t>
         </is>
       </c>
     </row>
@@ -19827,11 +19917,11 @@
         </is>
       </c>
       <c r="H527" t="n">
-        <v>240.4</v>
+        <v>746.6</v>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>257.9 (+7.3%)</t>
+          <t>257.865 (-65.5%)</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19942,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>327 (+5.8%)</t>
+          <t>324 (+4.9%)</t>
         </is>
       </c>
       <c r="F528" t="n">
@@ -19860,15 +19950,15 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>53193 (+4.5%)</t>
+          <t>52615 (+3.4%)</t>
         </is>
       </c>
       <c r="H528" t="n">
-        <v>229.2</v>
+        <v>741.8</v>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>239.0 (+4.3%)</t>
+          <t>256.425 (-65.4%)</t>
         </is>
       </c>
     </row>
@@ -19889,7 +19979,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>316 (+2.6%)</t>
+          <t>321 (+4.2%)</t>
         </is>
       </c>
       <c r="F529" t="n">
@@ -19897,15 +19987,15 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>61608 (+4.7%)</t>
+          <t>62749 (+6.6%)</t>
         </is>
       </c>
       <c r="H529" t="n">
-        <v>217.6</v>
+        <v>706.6</v>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>226.2 (+4.0%)</t>
+          <t>248.772 (-64.8%)</t>
         </is>
       </c>
     </row>
@@ -19938,11 +20028,11 @@
         </is>
       </c>
       <c r="H530" t="n">
-        <v>713.2</v>
+        <v>283.9</v>
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>685.5 (-3.9%)</t>
+          <t>857.511 (+202.0%)</t>
         </is>
       </c>
     </row>
@@ -19975,11 +20065,11 @@
         </is>
       </c>
       <c r="H531" t="n">
-        <v>698.4</v>
+        <v>678.1</v>
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>706.5 (+1.2%)</t>
+          <t>706.536 (+4.2%)</t>
         </is>
       </c>
     </row>
@@ -20012,11 +20102,11 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>508.4</v>
+        <v>966.6</v>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>514.6 (+1.2%)</t>
+          <t>514.603 (-46.8%)</t>
         </is>
       </c>
     </row>
@@ -20037,7 +20127,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>301 (+0.0%)</t>
+          <t>304 (+1.0%)</t>
         </is>
       </c>
       <c r="F533" t="n">
@@ -20045,15 +20135,15 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>16541 (+14.9%)</t>
+          <t>17112 (+18.9%)</t>
         </is>
       </c>
       <c r="H533" t="n">
-        <v>261.1</v>
+        <v>867.6</v>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>267.8 (+2.6%)</t>
+          <t>292.827 (-66.2%)</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20164,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>285 (+3.6%)</t>
+          <t>281 (+2.2%)</t>
         </is>
       </c>
       <c r="F534" t="n">
@@ -20082,15 +20172,15 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>34947 (+3.2%)</t>
+          <t>36682 (+8.3%)</t>
         </is>
       </c>
       <c r="H534" t="n">
-        <v>204</v>
+        <v>741.9</v>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>213.9 (+4.9%)</t>
+          <t>235.839 (-68.2%)</t>
         </is>
       </c>
     </row>
@@ -20119,15 +20209,15 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>44236 (+7.1%)</t>
+          <t>43331 (+4.9%)</t>
         </is>
       </c>
       <c r="H535" t="n">
-        <v>202.4</v>
+        <v>778.4</v>
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>204.4 (+1.0%)</t>
+          <t>232.191 (-70.2%)</t>
         </is>
       </c>
     </row>
@@ -20148,7 +20238,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>263 (+5.6%)</t>
+          <t>272 (+9.2%)</t>
         </is>
       </c>
       <c r="F536" t="n">
@@ -20156,15 +20246,15 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>51935 (+3.6%)</t>
+          <t>52210 (+4.1%)</t>
         </is>
       </c>
       <c r="H536" t="n">
-        <v>190</v>
+        <v>763</v>
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>199.3 (+4.9%)</t>
+          <t>214.098 (-71.9%)</t>
         </is>
       </c>
     </row>
@@ -20197,11 +20287,11 @@
         </is>
       </c>
       <c r="H537" t="n">
-        <v>874.3</v>
+        <v>347.9</v>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>350.1 (-60.0%)</t>
+          <t>350.14 (+0.6%)</t>
         </is>
       </c>
     </row>
@@ -20234,11 +20324,11 @@
         </is>
       </c>
       <c r="H538" t="n">
-        <v>754.8</v>
+        <v>591.1</v>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>745.3 (-1.3%)</t>
+          <t>745.285 (+26.1%)</t>
         </is>
       </c>
     </row>
@@ -20271,11 +20361,11 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>699.6</v>
+        <v>580.6</v>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>691.2 (-1.2%)</t>
+          <t>691.201 (+19.0%)</t>
         </is>
       </c>
     </row>
@@ -20308,11 +20398,11 @@
         </is>
       </c>
       <c r="H540" t="n">
-        <v>524.3</v>
+        <v>455.9</v>
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>551.4 (+5.2%)</t>
+          <t>551.4 (+20.9%)</t>
         </is>
       </c>
     </row>
@@ -20345,11 +20435,11 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>469.7</v>
+        <v>405.6</v>
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>478.8 (+1.9%)</t>
+          <t>478.8 (+18.0%)</t>
         </is>
       </c>
     </row>
@@ -20382,11 +20472,11 @@
         </is>
       </c>
       <c r="H542" t="n">
-        <v>448.6</v>
+        <v>386.1</v>
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>468.2 (+4.4%)</t>
+          <t>468.2 (+21.3%)</t>
         </is>
       </c>
     </row>
@@ -20419,11 +20509,11 @@
         </is>
       </c>
       <c r="H543" t="n">
-        <v>444.5</v>
+        <v>393</v>
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>467.6 (+5.2%)</t>
+          <t>467.6 (+19.0%)</t>
         </is>
       </c>
     </row>
@@ -20456,11 +20546,11 @@
         </is>
       </c>
       <c r="H544" t="n">
-        <v>2117.7</v>
+        <v>842.7</v>
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>872.6 (-58.8%)</t>
+          <t>872.587 (+3.5%)</t>
         </is>
       </c>
     </row>
@@ -20493,11 +20583,11 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>831</v>
+        <v>808.4</v>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>713.5 (-14.1%)</t>
+          <t>713.498 (-11.7%)</t>
         </is>
       </c>
     </row>
@@ -20530,11 +20620,11 @@
         </is>
       </c>
       <c r="H546" t="n">
-        <v>549.9</v>
+        <v>851.3</v>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>557.5 (+1.4%)</t>
+          <t>557.496 (-34.5%)</t>
         </is>
       </c>
     </row>
@@ -20567,11 +20657,11 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>417.2</v>
+        <v>680.6</v>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>406.9 (-2.5%)</t>
+          <t>406.946 (-40.2%)</t>
         </is>
       </c>
     </row>
@@ -20604,11 +20694,11 @@
         </is>
       </c>
       <c r="H548" t="n">
-        <v>357.2</v>
+        <v>600.4</v>
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>348.3 (-2.5%)</t>
+          <t>348.291 (-42.0%)</t>
         </is>
       </c>
     </row>
@@ -20641,11 +20731,11 @@
         </is>
       </c>
       <c r="H549" t="n">
-        <v>349.2</v>
+        <v>587.9</v>
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>344.4 (-1.4%)</t>
+          <t>344.379 (-41.4%)</t>
         </is>
       </c>
     </row>
@@ -20678,11 +20768,11 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>313.3</v>
+        <v>540.2</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>324.2 (+3.5%)</t>
+          <t>324.2 (-40.0%)</t>
         </is>
       </c>
     </row>
@@ -20715,11 +20805,11 @@
         </is>
       </c>
       <c r="H551" t="n">
-        <v>1922.7</v>
+        <v>765.4</v>
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>864.1 (-55.1%)</t>
+          <t>864.147 (+12.9%)</t>
         </is>
       </c>
     </row>
@@ -20752,11 +20842,11 @@
         </is>
       </c>
       <c r="H552" t="n">
-        <v>808</v>
+        <v>786.8</v>
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>705.9 (-12.6%)</t>
+          <t>705.945 (-10.3%)</t>
         </is>
       </c>
     </row>
@@ -20789,11 +20879,11 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>507.7</v>
+        <v>948.9</v>
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>518.7 (+2.2%)</t>
+          <t>518.72 (-45.3%)</t>
         </is>
       </c>
     </row>
@@ -20826,11 +20916,11 @@
         </is>
       </c>
       <c r="H554" t="n">
-        <v>340.6</v>
+        <v>805.1</v>
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>347.7 (+2.1%)</t>
+          <t>347.686 (-56.8%)</t>
         </is>
       </c>
     </row>
@@ -20851,7 +20941,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>406 (+0.7%)</t>
+          <t>412 (+2.2%)</t>
         </is>
       </c>
       <c r="F555" t="n">
@@ -20859,15 +20949,15 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>59110 (-0.1%)</t>
+          <t>59607 (+0.8%)</t>
         </is>
       </c>
       <c r="H555" t="n">
-        <v>276.3</v>
+        <v>685.6</v>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>290.3 (+5.1%)</t>
+          <t>307.6 (-55.1%)</t>
         </is>
       </c>
     </row>
@@ -20900,11 +20990,11 @@
         </is>
       </c>
       <c r="H556" t="n">
-        <v>276.6</v>
+        <v>674.7</v>
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>284.6 (+2.9%)</t>
+          <t>284.561 (-57.8%)</t>
         </is>
       </c>
     </row>
@@ -20937,11 +21027,11 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>277.7</v>
+        <v>697.7</v>
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>275.2 (-0.9%)</t>
+          <t>275.151 (-60.6%)</t>
         </is>
       </c>
     </row>
@@ -20974,11 +21064,11 @@
         </is>
       </c>
       <c r="H558" t="n">
-        <v>1954.1</v>
+        <v>777.3</v>
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>868.0 (-55.6%)</t>
+          <t>867.961 (+11.7%)</t>
         </is>
       </c>
     </row>
@@ -21011,11 +21101,11 @@
         </is>
       </c>
       <c r="H559" t="n">
-        <v>865.5</v>
+        <v>842.7</v>
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>721.5 (-16.6%)</t>
+          <t>721.46 (-14.4%)</t>
         </is>
       </c>
     </row>
@@ -21048,11 +21138,11 @@
         </is>
       </c>
       <c r="H560" t="n">
-        <v>507.4</v>
+        <v>964.6</v>
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>516.1 (+1.7%)</t>
+          <t>516.084 (-46.5%)</t>
         </is>
       </c>
     </row>
@@ -21085,11 +21175,11 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>307</v>
+        <v>905.7</v>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>300.7 (-2.1%)</t>
+          <t>300.738 (-66.8%)</t>
         </is>
       </c>
     </row>
@@ -21122,11 +21212,11 @@
         </is>
       </c>
       <c r="H562" t="n">
-        <v>241.3</v>
+        <v>758.9</v>
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>255.2 (+5.8%)</t>
+          <t>255.21 (-66.4%)</t>
         </is>
       </c>
     </row>
@@ -21159,11 +21249,11 @@
         </is>
       </c>
       <c r="H563" t="n">
-        <v>231.6</v>
+        <v>742.4</v>
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>252.8 (+9.2%)</t>
+          <t>252.754 (-66.0%)</t>
         </is>
       </c>
     </row>
@@ -21196,11 +21286,11 @@
         </is>
       </c>
       <c r="H564" t="n">
-        <v>242.1</v>
+        <v>754.3</v>
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>248.9 (+2.8%)</t>
+          <t>248.939 (-67.0%)</t>
         </is>
       </c>
     </row>
@@ -21233,11 +21323,11 @@
         </is>
       </c>
       <c r="H565" t="n">
-        <v>718.7</v>
+        <v>286</v>
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>706.9 (-1.6%)</t>
+          <t>865.703 (+202.7%)</t>
         </is>
       </c>
     </row>
@@ -21270,11 +21360,11 @@
         </is>
       </c>
       <c r="H566" t="n">
-        <v>760.8</v>
+        <v>740.8</v>
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>697.9 (-8.3%)</t>
+          <t>697.912 (-5.8%)</t>
         </is>
       </c>
     </row>
@@ -21307,11 +21397,11 @@
         </is>
       </c>
       <c r="H567" t="n">
-        <v>511.1</v>
+        <v>969.9</v>
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>521.8 (+2.1%)</t>
+          <t>521.8 (-46.2%)</t>
         </is>
       </c>
     </row>
@@ -21344,11 +21434,11 @@
         </is>
       </c>
       <c r="H568" t="n">
-        <v>277.5</v>
+        <v>937.5</v>
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>281.9 (+1.6%)</t>
+          <t>281.9 (-69.9%)</t>
         </is>
       </c>
     </row>
@@ -21381,11 +21471,11 @@
         </is>
       </c>
       <c r="H569" t="n">
-        <v>233.8</v>
+        <v>847.1</v>
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>234.8 (+0.4%)</t>
+          <t>234.8 (-72.3%)</t>
         </is>
       </c>
     </row>
@@ -21418,11 +21508,11 @@
         </is>
       </c>
       <c r="H570" t="n">
-        <v>215.4</v>
+        <v>844.8</v>
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>221.4 (+2.8%)</t>
+          <t>221.375 (-73.8%)</t>
         </is>
       </c>
     </row>
@@ -21455,11 +21545,11 @@
         </is>
       </c>
       <c r="H571" t="n">
-        <v>218.6</v>
+        <v>850.5</v>
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>219.4 (+0.4%)</t>
+          <t>219.4 (-74.2%)</t>
         </is>
       </c>
     </row>
